--- a/examples/create_scenario_with_market/scenario_with_market/agents.xlsx
+++ b/examples/create_scenario_with_market/scenario_with_market/agents.xlsx
@@ -2303,7 +2303,7 @@
       </c>
       <c r="HF2" t="inlineStr">
         <is>
-          <t>gurobi</t>
+          <t>highs</t>
         </is>
       </c>
       <c r="HG2" t="n">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="HK2" t="inlineStr">
         <is>
-          <t>gurobi</t>
+          <t>highs</t>
         </is>
       </c>
       <c r="HL2" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="HF3" t="inlineStr">
         <is>
-          <t>gurobi</t>
+          <t>highs</t>
         </is>
       </c>
       <c r="HG3" t="n">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="HK3" t="inlineStr">
         <is>
-          <t>gurobi</t>
+          <t>highs</t>
         </is>
       </c>
       <c r="HL3" t="n">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="HF4" t="inlineStr">
         <is>
-          <t>gurobi</t>
+          <t>highs</t>
         </is>
       </c>
       <c r="HG4" t="n">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="HK4" t="inlineStr">
         <is>
-          <t>gurobi</t>
+          <t>highs</t>
         </is>
       </c>
       <c r="HL4" t="n">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="HF5" t="inlineStr">
         <is>
-          <t>gurobi</t>
+          <t>highs</t>
         </is>
       </c>
       <c r="HG5" t="n">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="HK5" t="inlineStr">
         <is>
-          <t>gurobi</t>
+          <t>highs</t>
         </is>
       </c>
       <c r="HL5" t="n">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="HF6" t="inlineStr">
         <is>
-          <t>gurobi</t>
+          <t>highs</t>
         </is>
       </c>
       <c r="HG6" t="n">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="HK6" t="inlineStr">
         <is>
-          <t>gurobi</t>
+          <t>highs</t>
         </is>
       </c>
       <c r="HL6" t="n">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="HF7" t="inlineStr">
         <is>
-          <t>gurobi</t>
+          <t>highs</t>
         </is>
       </c>
       <c r="HG7" t="n">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="HK7" t="inlineStr">
         <is>
-          <t>gurobi</t>
+          <t>highs</t>
         </is>
       </c>
       <c r="HL7" t="n">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="HF8" t="inlineStr">
         <is>
-          <t>gurobi</t>
+          <t>highs</t>
         </is>
       </c>
       <c r="HG8" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="HK8" t="inlineStr">
         <is>
-          <t>gurobi</t>
+          <t>highs</t>
         </is>
       </c>
       <c r="HL8" t="n">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="HF9" t="inlineStr">
         <is>
-          <t>gurobi</t>
+          <t>highs</t>
         </is>
       </c>
       <c r="HG9" t="n">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="HK9" t="inlineStr">
         <is>
-          <t>gurobi</t>
+          <t>highs</t>
         </is>
       </c>
       <c r="HL9" t="n">
